--- a/artfynd/A 8955-2025 artfynd.xlsx
+++ b/artfynd/A 8955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852672</v>
+        <v>122852781</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>97319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -767,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852781</v>
+        <v>122852672</v>
       </c>
       <c r="B3" t="n">
-        <v>97319</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -823,9 +824,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -877,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8955-2025 artfynd.xlsx
+++ b/artfynd/A 8955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852781</v>
+        <v>122852672</v>
       </c>
       <c r="B2" t="n">
-        <v>97319</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -767,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852672</v>
+        <v>122852781</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>97319</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,9 +823,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -878,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8955-2025 artfynd.xlsx
+++ b/artfynd/A 8955-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122852672</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>122852781</v>
       </c>
       <c r="B3" t="n">
-        <v>97319</v>
+        <v>97322</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8955-2025 artfynd.xlsx
+++ b/artfynd/A 8955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852672</v>
+        <v>122852781</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>97324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -767,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852781</v>
+        <v>122852672</v>
       </c>
       <c r="B3" t="n">
-        <v>97322</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -823,9 +824,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -877,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8955-2025 artfynd.xlsx
+++ b/artfynd/A 8955-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122852781</v>
       </c>
       <c r="B2" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 8955-2025 artfynd.xlsx
+++ b/artfynd/A 8955-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122852672</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>122852781</v>
       </c>
       <c r="B3" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8955-2025 artfynd.xlsx
+++ b/artfynd/A 8955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852672</v>
+        <v>122852781</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>97367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -767,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852781</v>
+        <v>122852672</v>
       </c>
       <c r="B3" t="n">
-        <v>97350</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -823,9 +824,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -877,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8955-2025 artfynd.xlsx
+++ b/artfynd/A 8955-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122852781</v>
       </c>
       <c r="B2" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>122852672</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
